--- a/output/pdf_financials_xlsx/BNE.xlsx
+++ b/output/pdf_financials_xlsx/BNE.xlsx
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>2.02</v>
+        <v>7.722</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0.002662</v>
@@ -6624,46 +6624,46 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000309</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.182</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-3.6e-05</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000402</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000479</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>0.828</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000244</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.001621</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002569</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-1.222</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.00119</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002304</v>
       </c>
     </row>
     <row r="119">
@@ -32314,7 +32314,11 @@
           <t>Exploration and evaluation expenditures 5</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -34179,7 +34183,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -36485,7 +36493,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -37985,7 +37997,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -39326,7 +39342,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -41191,7 +41211,11 @@
           <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -41642,7 +41666,11 @@
           <t>Exploration and evaluation expenses</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -42714,7 +42742,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -45547,7 +45579,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BNE.xlsx
+++ b/output/pdf_financials_xlsx/BNE.xlsx
@@ -1244,7 +1244,7 @@
         <v>-0.010505</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.011062</v>
+        <v>0.000355</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.003547</v>
@@ -2032,7 +2032,7 @@
         <v>9.58546622503262</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>558.1231079717458</v>
+        <v>17.91120080726539</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-11.88433960999799</v>
@@ -3769,22 +3769,22 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.02589</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>20.181</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.018966</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.01517</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.01513</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.01871</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>19.547</v>
@@ -3793,22 +3793,22 @@
         <v>14.489</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>15.744</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.02542</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.027701</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>30.625</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>24.294</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>23.685</v>
       </c>
     </row>
     <row r="65">
@@ -3925,22 +3925,22 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.004826</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>8.420999999999999</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.015295</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.016669</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.005349</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.006526</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>6.583</v>
@@ -3949,22 +3949,22 @@
         <v>4.254</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>9.679</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.009774</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.007872000000000001</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>6.601</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>12.077</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>13.451</v>
       </c>
     </row>
     <row r="68">
@@ -4001,7 +4001,7 @@
         <v>18.743</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>25.423</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0.035194</v>
@@ -6465,25 +6465,25 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>5.603</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.003991</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>3.485</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.000968</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.001539</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.00813</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.010783</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -6504,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.001448</v>
       </c>
       <c r="P115" s="3" t="n">
         <v>0</v>
@@ -6819,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-0.002667</v>
       </c>
     </row>
     <row r="122">
@@ -30428,7 +30428,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -31976,7 +31980,11 @@
           <t>Repurchase of common shares 12</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -32668,7 +32676,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -33402,7 +33414,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -34436,7 +34452,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -35152,7 +35172,11 @@
           <t>Deferred income taxes expense</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -39611,7 +39635,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -40038,7 +40066,11 @@
           <t>Issuance of common shares by private placement</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -45852,7 +45884,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E429" s="5" t="n">
         <v>5.603</v>
       </c>
@@ -47426,7 +47462,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -57086,7 +57126,11 @@
           <t>Current income tax (recovery) 16</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E555" t="inlineStr">
         <is>
           <t>-</t>
